--- a/src/main/resources/espacios/0 Step/0 - There.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - There.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 There" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="710">
   <si>
     <t xml:space="preserve">There is</t>
   </si>
@@ -33,16 +33,16 @@
     <t xml:space="preserve">ðɛr ɪz</t>
   </si>
   <si>
+    <t xml:space="preserve">There is a cat in the tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay un gato en el árbol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɛr ɪz ə kæt ɪn ðə tri</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXAMPLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is a cat in the tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hay un gato en el árbol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ðɛr ɪz ə kæt ɪn ðə tri</t>
   </si>
   <si>
     <t xml:space="preserve">There is a book on the table</t>
@@ -2373,7 +2373,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F96"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48.52"/>
@@ -2392,22 +2392,20 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2421,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2435,7 +2433,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2449,7 +2447,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2463,7 +2461,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2477,7 +2475,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2491,7 +2489,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2505,7 +2503,7 @@
         <v>27</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2519,7 +2517,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2533,7 +2531,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2547,7 +2545,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2561,7 +2559,7 @@
         <v>39</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2575,7 +2573,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2589,7 +2587,7 @@
         <v>45</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2603,7 +2601,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2629,7 +2627,7 @@
         <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2643,7 +2641,7 @@
         <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2657,7 +2655,7 @@
         <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2671,7 +2669,7 @@
         <v>62</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2685,7 +2683,7 @@
         <v>65</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2699,7 +2697,7 @@
         <v>68</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2713,7 +2711,7 @@
         <v>71</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2727,7 +2725,7 @@
         <v>74</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2741,7 +2739,7 @@
         <v>77</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2755,7 +2753,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2769,7 +2767,7 @@
         <v>83</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2783,7 +2781,7 @@
         <v>86</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2797,7 +2795,7 @@
         <v>89</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2811,7 +2809,7 @@
         <v>92</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2825,7 +2823,7 @@
         <v>95</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2839,7 +2837,7 @@
         <v>98</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2853,7 +2851,7 @@
         <v>101</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2867,7 +2865,7 @@
         <v>104</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2881,7 +2879,7 @@
         <v>107</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2895,7 +2893,7 @@
         <v>110</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2909,7 +2907,7 @@
         <v>113</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2923,7 +2921,7 @@
         <v>116</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2937,7 +2935,7 @@
         <v>119</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2951,7 +2949,7 @@
         <v>122</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2965,7 +2963,7 @@
         <v>125</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2979,7 +2977,7 @@
         <v>128</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2993,7 +2991,7 @@
         <v>131</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3007,7 +3005,7 @@
         <v>134</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,7 +3019,7 @@
         <v>137</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3035,7 +3033,7 @@
         <v>140</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3049,7 +3047,7 @@
         <v>143</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3075,7 +3073,7 @@
         <v>149</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3089,7 +3087,7 @@
         <v>152</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3103,7 +3101,7 @@
         <v>155</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,7 +3115,7 @@
         <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3131,7 +3129,7 @@
         <v>161</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3145,7 +3143,7 @@
         <v>164</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3159,7 +3157,7 @@
         <v>167</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3173,7 +3171,7 @@
         <v>170</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3187,7 +3185,7 @@
         <v>173</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3201,7 +3199,7 @@
         <v>176</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3215,7 +3213,7 @@
         <v>179</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3229,7 +3227,7 @@
         <v>182</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3243,7 +3241,7 @@
         <v>185</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3257,7 +3255,7 @@
         <v>188</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3271,7 +3269,7 @@
         <v>191</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3297,7 +3295,7 @@
         <v>196</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,7 +3309,7 @@
         <v>199</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3325,7 +3323,7 @@
         <v>202</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3339,7 +3337,7 @@
         <v>205</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3353,7 +3351,7 @@
         <v>208</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3367,7 +3365,7 @@
         <v>211</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3381,7 +3379,7 @@
         <v>214</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3395,7 +3393,7 @@
         <v>217</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3409,7 +3407,7 @@
         <v>220</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3423,7 +3421,7 @@
         <v>223</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3437,7 +3435,7 @@
         <v>226</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3451,7 +3449,7 @@
         <v>229</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3465,7 +3463,7 @@
         <v>232</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3479,7 +3477,7 @@
         <v>235</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3493,7 +3491,7 @@
         <v>238</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3519,7 +3517,7 @@
         <v>243</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3533,7 +3531,7 @@
         <v>246</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3547,7 +3545,7 @@
         <v>249</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3561,7 +3559,7 @@
         <v>252</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3575,7 +3573,7 @@
         <v>255</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3589,7 +3587,7 @@
         <v>258</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3603,7 +3601,7 @@
         <v>261</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3617,7 +3615,7 @@
         <v>264</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3631,7 +3629,7 @@
         <v>267</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3645,7 +3643,7 @@
         <v>270</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3659,7 +3657,7 @@
         <v>273</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3673,7 +3671,7 @@
         <v>276</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3687,7 +3685,7 @@
         <v>279</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3701,7 +3699,7 @@
         <v>282</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3715,7 +3713,7 @@
         <v>285</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3735,7 +3733,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="105.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.13"/>
@@ -3766,7 +3764,7 @@
         <v>291</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3780,7 +3778,7 @@
         <v>294</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3794,7 +3792,7 @@
         <v>297</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3808,7 +3806,7 @@
         <v>300</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3822,7 +3820,7 @@
         <v>303</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3836,7 +3834,7 @@
         <v>306</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3850,7 +3848,7 @@
         <v>309</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3864,7 +3862,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3878,7 +3876,7 @@
         <v>315</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3892,7 +3890,7 @@
         <v>318</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3906,7 +3904,7 @@
         <v>321</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3920,7 +3918,7 @@
         <v>324</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3934,7 +3932,7 @@
         <v>327</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3948,7 +3946,7 @@
         <v>330</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3962,7 +3960,7 @@
         <v>333</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3988,7 +3986,7 @@
         <v>229</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4002,7 +4000,7 @@
         <v>337</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4016,7 +4014,7 @@
         <v>340</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4030,7 +4028,7 @@
         <v>343</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,7 +4042,7 @@
         <v>346</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4058,7 +4056,7 @@
         <v>349</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4072,7 +4070,7 @@
         <v>352</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4086,7 +4084,7 @@
         <v>355</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4100,7 +4098,7 @@
         <v>358</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4114,7 +4112,7 @@
         <v>361</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4128,7 +4126,7 @@
         <v>364</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4142,7 +4140,7 @@
         <v>367</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4156,7 +4154,7 @@
         <v>370</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4170,7 +4168,7 @@
         <v>373</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4184,7 +4182,7 @@
         <v>376</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4209,7 +4207,7 @@
         <v>382</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4223,7 +4221,7 @@
         <v>385</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4237,7 +4235,7 @@
         <v>388</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,7 +4249,7 @@
         <v>391</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4265,7 +4263,7 @@
         <v>394</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4279,7 +4277,7 @@
         <v>397</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4293,7 +4291,7 @@
         <v>400</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4307,7 +4305,7 @@
         <v>403</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4321,7 +4319,7 @@
         <v>406</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4335,7 +4333,7 @@
         <v>409</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4349,7 +4347,7 @@
         <v>412</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4363,7 +4361,7 @@
         <v>415</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4377,7 +4375,7 @@
         <v>418</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4391,7 +4389,7 @@
         <v>421</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4405,7 +4403,7 @@
         <v>424</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,7 +4428,7 @@
         <v>430</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4444,7 +4442,7 @@
         <v>433</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4458,7 +4456,7 @@
         <v>436</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4472,7 +4470,7 @@
         <v>439</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4486,7 +4484,7 @@
         <v>442</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4500,7 +4498,7 @@
         <v>445</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4514,7 +4512,7 @@
         <v>448</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4528,7 +4526,7 @@
         <v>451</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4542,7 +4540,7 @@
         <v>454</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4556,7 +4554,7 @@
         <v>457</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4570,7 +4568,7 @@
         <v>460</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4584,7 +4582,7 @@
         <v>463</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4598,7 +4596,7 @@
         <v>466</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4612,7 +4610,7 @@
         <v>469</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4626,7 +4624,7 @@
         <v>472</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4646,7 +4644,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="65.85"/>
@@ -4677,7 +4675,7 @@
         <v>478</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4691,7 +4689,7 @@
         <v>481</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4705,7 +4703,7 @@
         <v>484</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4719,7 +4717,7 @@
         <v>487</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4733,7 +4731,7 @@
         <v>490</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4747,7 +4745,7 @@
         <v>493</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4761,7 +4759,7 @@
         <v>496</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4775,7 +4773,7 @@
         <v>499</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4789,7 +4787,7 @@
         <v>502</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4803,7 +4801,7 @@
         <v>505</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4817,7 +4815,7 @@
         <v>508</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4831,7 +4829,7 @@
         <v>511</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4845,7 +4843,7 @@
         <v>514</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4859,7 +4857,7 @@
         <v>517</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4873,7 +4871,7 @@
         <v>520</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4898,7 +4896,7 @@
         <v>525</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4912,7 +4910,7 @@
         <v>528</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4926,7 +4924,7 @@
         <v>531</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4940,7 +4938,7 @@
         <v>534</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4954,7 +4952,7 @@
         <v>537</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4968,7 +4966,7 @@
         <v>540</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4982,7 +4980,7 @@
         <v>543</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4996,7 +4994,7 @@
         <v>546</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5010,7 +5008,7 @@
         <v>549</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5024,7 +5022,7 @@
         <v>552</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5038,7 +5036,7 @@
         <v>555</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5052,7 +5050,7 @@
         <v>558</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5066,7 +5064,7 @@
         <v>561</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5080,7 +5078,7 @@
         <v>564</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5094,7 +5092,7 @@
         <v>567</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5119,7 +5117,7 @@
         <v>573</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5133,7 +5131,7 @@
         <v>576</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5147,7 +5145,7 @@
         <v>579</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5161,7 +5159,7 @@
         <v>582</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5175,7 +5173,7 @@
         <v>585</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5189,7 +5187,7 @@
         <v>588</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5203,7 +5201,7 @@
         <v>591</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5217,7 +5215,7 @@
         <v>594</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5231,7 +5229,7 @@
         <v>597</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5245,7 +5243,7 @@
         <v>600</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5259,7 +5257,7 @@
         <v>603</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5273,7 +5271,7 @@
         <v>606</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5287,7 +5285,7 @@
         <v>609</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5301,7 +5299,7 @@
         <v>612</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5315,7 +5313,7 @@
         <v>615</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5340,7 +5338,7 @@
         <v>620</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5354,7 +5352,7 @@
         <v>623</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5368,7 +5366,7 @@
         <v>626</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5382,7 +5380,7 @@
         <v>629</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5396,7 +5394,7 @@
         <v>632</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5410,7 +5408,7 @@
         <v>634</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5424,7 +5422,7 @@
         <v>637</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5438,7 +5436,7 @@
         <v>640</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5452,7 +5450,7 @@
         <v>643</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5466,7 +5464,7 @@
         <v>646</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5480,7 +5478,7 @@
         <v>649</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,7 +5492,7 @@
         <v>652</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5508,7 +5506,7 @@
         <v>655</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5522,7 +5520,7 @@
         <v>658</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5536,7 +5534,7 @@
         <v>661</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,7 +5559,7 @@
         <v>667</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5575,7 +5573,7 @@
         <v>670</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,7 +5587,7 @@
         <v>673</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5603,7 +5601,7 @@
         <v>676</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5617,7 +5615,7 @@
         <v>679</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5631,7 +5629,7 @@
         <v>682</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5645,7 +5643,7 @@
         <v>685</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,7 +5657,7 @@
         <v>688</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5673,7 +5671,7 @@
         <v>691</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5687,7 +5685,7 @@
         <v>694</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5701,7 +5699,7 @@
         <v>697</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5715,7 +5713,7 @@
         <v>700</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5729,7 +5727,7 @@
         <v>703</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5743,7 +5741,7 @@
         <v>706</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5757,7 +5755,7 @@
         <v>709</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/espacios/0 Step/0 - There.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - There.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="711">
   <si>
     <t xml:space="preserve">There is</t>
   </si>
@@ -42,16 +42,19 @@
     <t xml:space="preserve">ðɛr ɪz ə kæt ɪn ðə tri</t>
   </si>
   <si>
+    <t xml:space="preserve">HEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is a book on the table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay un libro en la mesa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɛr ɪz ə bʊk ɑn ðə ˈteɪbəl</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXAMPLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is a book on the table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hay un libro en la mesa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ðɛr ɪz ə bʊk ɑn ðə ˈteɪbəl</t>
   </si>
   <si>
     <t xml:space="preserve">There is a car in the garage</t>
@@ -2419,422 +2422,424 @@
         <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
@@ -2842,111 +2847,111 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
@@ -2954,766 +2959,772 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F65" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F81" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3744,24 +3755,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -3769,862 +3780,870 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4655,24 +4674,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -4680,1082 +4699,1094 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
